--- a/cenik.xlsx
+++ b/cenik.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9253F97B-E2C3-4A81-BA29-3A3195204623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8E6266-C4DD-444B-900E-5E9E0ED04D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11040" yWindow="630" windowWidth="20910" windowHeight="11730" xr2:uid="{C41A15B1-AF4B-4EE8-ABE4-E931C9C78A17}"/>
+    <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{C41A15B1-AF4B-4EE8-ABE4-E931C9C78A17}"/>
   </bookViews>
   <sheets>
     <sheet name="cenik" sheetId="2" r:id="rId1"/>
@@ -211,9 +211,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motiv Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motiv Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 –⁠ 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -251,7 +251,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 –⁠ 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -357,7 +357,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 –⁠ 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -499,7 +499,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -542,10 +542,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="C3" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -553,10 +553,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C4" s="1">
-        <v>1000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -564,10 +564,10 @@
         <v>8</v>
       </c>
       <c r="B5" s="1">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="C5" s="1">
-        <v>1350</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -575,10 +575,10 @@
         <v>9</v>
       </c>
       <c r="B6" s="1">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="C6" s="1">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -586,10 +586,10 @@
         <v>10</v>
       </c>
       <c r="B7" s="1">
-        <v>1650</v>
+        <v>1800</v>
       </c>
       <c r="C7" s="1">
-        <v>1900</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -597,10 +597,10 @@
         <v>11</v>
       </c>
       <c r="B8" s="1">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="C8" s="1">
-        <v>2100</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -608,7 +608,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="1">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
@@ -619,7 +619,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="1">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
@@ -688,7 +688,7 @@
         <v>1200</v>
       </c>
       <c r="C16" s="1">
-        <v>1600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -718,10 +718,10 @@
         <v>6</v>
       </c>
       <c r="B19" s="1">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="C19" s="1">
-        <v>10500</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -729,10 +729,10 @@
         <v>7</v>
       </c>
       <c r="B20" s="1">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="C20" s="1">
-        <v>15000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -740,10 +740,10 @@
         <v>8</v>
       </c>
       <c r="B21" s="1">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="C21" s="1">
-        <v>18000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -773,7 +773,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="1">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="C24" s="1">
         <v>250</v>
@@ -784,7 +784,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="1">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="C25" s="1">
         <v>270</v>
@@ -795,7 +795,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="1">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="C26" s="1">
         <v>300</v>
